--- a/dataset_t6_grouped/results2/G3/G3_T2677_W0056F0001T0006Z000C1N25_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T2677_W0056F0001T0006Z000C1N25_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>28.12155581422828</v>
+        <v>4.569752819812095</v>
       </c>
       <c r="D2" t="n">
-        <v>34.01210933964058</v>
+        <v>5.526967767691595</v>
       </c>
       <c r="E2" t="n">
-        <v>4.329589171059682</v>
+        <v>0.7035582402971987</v>
       </c>
       <c r="F2" t="n">
-        <v>1.490971534708553</v>
+        <v>0.2422828743901397</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>36.78073415634764</v>
+        <v>5.976869300406492</v>
       </c>
       <c r="D3" t="n">
-        <v>36.99405240905769</v>
+        <v>6.011533516471874</v>
       </c>
       <c r="E3" t="n">
-        <v>4.329589171059682</v>
+        <v>0.7035582402971987</v>
       </c>
       <c r="F3" t="n">
-        <v>1.490971534708553</v>
+        <v>0.2422828743901397</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
